--- a/measurements/24/Filled_2D_sections/coronal/week24_coronal_Batch_Allmarks.xlsx
+++ b/measurements/24/Filled_2D_sections/coronal/week24_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,67 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +561,70 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.13979773944081</v>
+        <v>1578.004535147392</v>
       </c>
       <c r="D2" t="n">
-        <v>10.75166639176811</v>
+        <v>209.9134866964249</v>
       </c>
       <c r="E2" t="n">
-        <v>9.344386289759381</v>
+        <v>182.4380180381593</v>
       </c>
       <c r="F2" t="n">
         <v>1.150601661614844</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4500258141475768</v>
+        <v>0.4500258141475766</v>
       </c>
       <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.824032738095238</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.978050595238095</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.5365853658536586</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.576219512195122</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.5564024390243902</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10.47619047619048</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.704985119047619</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.635044642857143</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.824032738095238</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>4.191894705532421</v>
+      <c r="Z2" s="2" t="n">
+        <v>1597.862811791383</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +635,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.186198691255205</v>
+        <v>1595.691609977324</v>
       </c>
       <c r="D3" t="n">
-        <v>10.80044686794281</v>
+        <v>210.8658674217406</v>
       </c>
       <c r="E3" t="n">
-        <v>9.42174172110674</v>
+        <v>183.9482907454173</v>
       </c>
       <c r="F3" t="n">
         <v>1.146332301144222</v>
@@ -572,24 +654,51 @@
         <v>0.450968546163028</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5422065548780488</v>
+        <v>0.824032738095238</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5422065548780488</v>
+        <v>10.5859375</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5422065548780488</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>5.821056547619047</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10.5859375</v>
+      </c>
+      <c r="N3" t="n">
+        <v>9.047619047619047</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6.1328125</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.514880952380952</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.824032738095238</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>10.81868262770699</v>
+      <c r="Z3" s="2" t="n">
+        <v>211.2218989218984</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +709,70 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.212968471148126</v>
+        <v>1605.895691609977</v>
       </c>
       <c r="D4" t="n">
-        <v>10.93841891172456</v>
+        <v>213.5596073241461</v>
       </c>
       <c r="E4" t="n">
-        <v>9.484809686497945</v>
+        <v>185.1796176887694</v>
       </c>
       <c r="F4" t="n">
         <v>1.153256551609664</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4424752361294914</v>
+        <v>0.4424752361294915</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5421112804878049</v>
+        <v>0.8147321428571428</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5421112804878049</v>
+        <v>10.58407738095238</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5421112804878049</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>5.984747023809524</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10.58407738095238</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8.844866071428571</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.6015625</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.078497023809524</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8147321428571428</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>9.4149026001372</v>
+      <c r="Z4" s="2" t="n">
+        <v>183.8147650502977</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +783,66 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.233789411064842</v>
+        <v>1613.832199546485</v>
       </c>
       <c r="D5" t="n">
-        <v>10.90637727481563</v>
+        <v>212.9340325083051</v>
       </c>
       <c r="E5" t="n">
-        <v>9.499097172806904</v>
+        <v>185.4585638500395</v>
       </c>
       <c r="F5" t="n">
-        <v>1.148148826820863</v>
+        <v>1.148148826820864</v>
       </c>
       <c r="G5" t="n">
         <v>0.4472785618451297</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5257240853658537</v>
+        <v>3.597470238095238</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5257240853658537</v>
+        <v>10.2641369047619</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5257240853658537</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>7.00009300595238</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10.2641369047619</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7.447916666666666</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6.690848214285714</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.597470238095238</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Z5" s="2" t="n">
         <v>1.148838685444346</v>
       </c>
     </row>
@@ -694,17 +854,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.232599643069602</v>
+        <v>1613.378684807256</v>
       </c>
       <c r="D6" t="n">
-        <v>11.0645548512296</v>
+        <v>216.0222613811493</v>
       </c>
       <c r="E6" t="n">
-        <v>9.499097155361641</v>
+        <v>185.4585635094415</v>
       </c>
       <c r="F6" t="n">
         <v>1.164800682661126</v>
@@ -713,23 +873,50 @@
         <v>0.4344593647074266</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5483041158536586</v>
+        <v>0.8649553571428571</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5483041158536586</v>
+        <v>10.70498511904762</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5483041158536586</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>6.235491071428571</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10.70498511904762</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7.457217261904762</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.116815476190475</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.033482142857142</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.8649553571428571</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Z6" s="2" t="n">
         <v>0.4508924683129573</v>
       </c>
     </row>
@@ -741,43 +928,70 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.246579417013683</v>
+        <v>1618.707482993197</v>
       </c>
       <c r="D7" t="n">
-        <v>11.23701991976761</v>
+        <v>219.3894365287962</v>
       </c>
       <c r="E7" t="n">
-        <v>9.574001245382355</v>
+        <v>186.9209766955603</v>
       </c>
       <c r="F7" t="n">
         <v>1.173701531027829</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4226168541957872</v>
+        <v>0.4226168541957873</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.547827743902439</v>
+        <v>0.8798363095238094</v>
       </c>
       <c r="J7" t="n">
-        <v>0.547827743902439</v>
+        <v>10.69568452380952</v>
       </c>
       <c r="K7" t="n">
-        <v>0.547827743902439</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>6.425967261904762</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10.69568452380952</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7.756696428571428</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7.202380952380952</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.595238095238095</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.8798363095238094</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>1.05</v>
+      <c r="Z7" s="2" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1002,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.265020820939917</v>
+        <v>1625.736961451247</v>
       </c>
       <c r="D8" t="n">
-        <v>11.13945896451066</v>
+        <v>217.4846750213986</v>
       </c>
       <c r="E8" t="n">
-        <v>9.559713782333747</v>
+        <v>186.6420309884207</v>
       </c>
       <c r="F8" t="n">
         <v>1.16525025938499</v>
@@ -807,24 +1021,48 @@
         <v>0.4319195119257161</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5472560975609756</v>
+        <v>5.658482142857142</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5472560975609756</v>
+        <v>10.68452380952381</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5472560975609756</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>7.744140625</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10.68452380952381</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7.431175595238095</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7.202380952380952</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5.658482142857142</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.5452743902439025</v>
+      <c r="Z8" s="2" t="n">
+        <v>4.084635416666666</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1073,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.253718024985128</v>
+        <v>1621.428571428571</v>
       </c>
       <c r="D9" t="n">
-        <v>11.21681436969013</v>
+        <v>218.9949472177596</v>
       </c>
       <c r="E9" t="n">
-        <v>9.574001242474813</v>
+        <v>186.9209766387939</v>
       </c>
       <c r="F9" t="n">
         <v>1.171591071027547</v>
@@ -854,24 +1092,48 @@
         <v>0.4248537894178244</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0.546875</v>
+        <v>6.584821428571428</v>
       </c>
       <c r="J9" t="n">
-        <v>0.546875</v>
+        <v>10.67708333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>0.546875</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>7.948753720238095</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10.67708333333333</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7.457217261904762</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7.075892857142857</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6.584821428571428</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.5472560975609756</v>
+      <c r="Z9" s="2" t="n">
+        <v>10.68452380952381</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1144,67 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.265913146936348</v>
+        <v>1626.077097505669</v>
       </c>
       <c r="D10" t="n">
-        <v>11.07292427667757</v>
+        <v>216.1856644494193</v>
       </c>
       <c r="E10" t="n">
-        <v>9.642987286172263</v>
+        <v>188.2678470157442</v>
       </c>
       <c r="F10" t="n">
         <v>1.148287760635731</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4372171743614181</v>
+        <v>0.4372171743614182</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5553544207317074</v>
+        <v>6.03422619047619</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5553544207317074</v>
+        <v>10.84263392857143</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5553544207317074</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>7.741350446428571</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10.84263392857143</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7.139136904761904</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.949404761904762</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6.03422619047619</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.546265243902439</v>
+      <c r="Z10" s="2" t="n">
+        <v>6.978483072916665</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1215,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.266508030933968</v>
+        <v>1626.303854875283</v>
       </c>
       <c r="D11" t="n">
-        <v>11.04434929533703</v>
+        <v>215.62777195658</v>
       </c>
       <c r="E11" t="n">
-        <v>9.642987268727001</v>
+        <v>188.2678466751462</v>
       </c>
       <c r="F11" t="n">
         <v>1.145324471303074</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4395438061744444</v>
+        <v>0.4395438061744446</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5568788109756098</v>
+        <v>6.037946428571428</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5568788109756098</v>
+        <v>10.87239583333333</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5568788109756098</v>
+        <v>7.811104910714286</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10.87239583333333</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.282366071428571</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7.051711309523809</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.037946428571428</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1286,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.259964306960143</v>
+        <v>1623.809523809524</v>
       </c>
       <c r="D12" t="n">
-        <v>11.19415749863881</v>
+        <v>218.5525987829481</v>
       </c>
       <c r="E12" t="n">
-        <v>9.579919329503689</v>
+        <v>187.036520242691</v>
       </c>
       <c r="F12" t="n">
         <v>1.168502271638518</v>
@@ -987,16 +1305,48 @@
         <v>0.4272017256059244</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5731707317073171</v>
+        <v>5.552455357142857</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5731707317073171</v>
+        <v>11.19047619047619</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5731707317073171</v>
+        <v>7.781808035714286</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11.19047619047619</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.230282738095238</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.154017857142857</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5.552455357142857</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>10.68452380952381</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1357,67 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.264425936942296</v>
+        <v>1625.510204081633</v>
       </c>
       <c r="D13" t="n">
-        <v>11.10251460715038</v>
+        <v>216.7633804253169</v>
       </c>
       <c r="E13" t="n">
-        <v>9.508481950294682</v>
+        <v>185.6417904581342</v>
       </c>
       <c r="F13" t="n">
-        <v>1.167643233187848</v>
+        <v>1.167643233187849</v>
       </c>
       <c r="G13" t="n">
         <v>0.4347381307487712</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5745998475609756</v>
+        <v>5.543154761904762</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5745998475609756</v>
+        <v>11.21837797619048</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5745998475609756</v>
+        <v>7.743675595238096</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11.21837797619048</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.150297619047619</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7.062872023809524</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5.543154761904762</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>9.456225198412699</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1428,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.259666864961333</v>
+        <v>1623.696145124716</v>
       </c>
       <c r="D14" t="n">
-        <v>10.95617312629049</v>
+        <v>213.9062372275761</v>
       </c>
       <c r="E14" t="n">
-        <v>9.431126504409605</v>
+        <v>184.1315174670446</v>
       </c>
       <c r="F14" t="n">
         <v>1.16170354847513</v>
@@ -1065,16 +1447,48 @@
         <v>0.4459310644170855</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5710746951219512</v>
+        <v>5.05766369047619</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5710746951219512</v>
+        <v>11.14955357142857</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5710746951219512</v>
+        <v>7.559523809523809</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11.14955357142857</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7.120535714285714</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6.910342261904762</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5.05766369047619</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1499,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.236763831052945</v>
+        <v>1614.965986394558</v>
       </c>
       <c r="D15" t="n">
-        <v>10.8122829780346</v>
+        <v>211.0969533806755</v>
       </c>
       <c r="E15" t="n">
-        <v>9.376427949928656</v>
+        <v>183.0635933081309</v>
       </c>
       <c r="F15" t="n">
         <v>1.153134545028618</v>
@@ -1104,16 +1518,48 @@
         <v>0.455417078471023</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>0.571265243902439</v>
+        <v>5.518973214285714</v>
       </c>
       <c r="J15" t="n">
-        <v>0.571265243902439</v>
+        <v>11.15327380952381</v>
       </c>
       <c r="K15" t="n">
-        <v>0.571265243902439</v>
+        <v>7.532552083333333</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11.15327380952381</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6.754092261904762</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6.703869047619047</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5.518973214285714</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>6.735770089285714</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1570,67 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.213860797144557</v>
+        <v>1606.235827664399</v>
       </c>
       <c r="D16" t="n">
-        <v>10.74921503881129</v>
+        <v>209.8656269482204</v>
       </c>
       <c r="E16" t="n">
-        <v>9.327647465031323</v>
+        <v>182.1112124125163</v>
       </c>
       <c r="F16" t="n">
         <v>1.152403655810248</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4582859539265088</v>
+        <v>0.4582859539265087</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5609756097560976</v>
+        <v>5.01860119047619</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5609756097560976</v>
+        <v>10.95238095238095</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5609756097560976</v>
+        <v>7.262369791666666</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>10.95238095238095</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6.58110119047619</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6.497395833333333</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5.01860119047619</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>6.415447255291005</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1641,67 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.185008923259964</v>
+        <v>1595.238095238095</v>
       </c>
       <c r="D17" t="n">
-        <v>10.47918900629369</v>
+        <v>204.5936901228768</v>
       </c>
       <c r="E17" t="n">
-        <v>9.327647459216234</v>
+        <v>182.1112122989836</v>
       </c>
       <c r="F17" t="n">
         <v>1.123454660150097</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4789066915904784</v>
+        <v>0.4789066915904785</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5365853658536586</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5365853658536586</v>
+        <v>10.47619047619048</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5365853658536586</v>
+        <v>6.980096726190475</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10.47619047619048</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6.34672619047619</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6.335565476190476</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>5.183167016806722</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1712,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.113920285544319</v>
+        <v>1568.140589569161</v>
       </c>
       <c r="D18" t="n">
-        <v>10.30672393775568</v>
+        <v>201.2265149752299</v>
       </c>
       <c r="E18" t="n">
-        <v>9.215799035095587</v>
+        <v>179.9275049709138</v>
       </c>
       <c r="F18" t="n">
         <v>1.118375509112735</v>
@@ -1221,16 +1731,48 @@
         <v>0.4866586518657063</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>0.522484756097561</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="J18" t="n">
-        <v>0.522484756097561</v>
+        <v>10.20089285714286</v>
       </c>
       <c r="K18" t="n">
-        <v>0.522484756097561</v>
+        <v>6.718284970238096</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10.20089285714286</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6.004464285714286</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.905877976190476</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +1783,67 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.061273051754908</v>
+        <v>1548.072562358277</v>
       </c>
       <c r="D19" t="n">
-        <v>10.23181980702935</v>
+        <v>199.7641009943826</v>
       </c>
       <c r="E19" t="n">
-        <v>9.140894910184349</v>
+        <v>178.4650911035992</v>
       </c>
       <c r="F19" t="n">
         <v>1.119345524433231</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4874906462988246</v>
+        <v>0.4874906462988245</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5218178353658537</v>
+        <v>4.611235119047619</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5218178353658537</v>
+        <v>10.18787202380952</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5218178353658537</v>
+        <v>6.599237351190476</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10.18787202380952</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>5.805431547619047</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.792410714285714</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.611235119047619</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>1.341889880952381</v>
       </c>
     </row>
     <row r="20">
@@ -1280,35 +1854,67 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.005056513979774</v>
+        <v>1526.643990929705</v>
       </c>
       <c r="D20" t="n">
-        <v>10.20916295633083</v>
+        <v>199.3217529569353</v>
       </c>
       <c r="E20" t="n">
-        <v>9.098032526853608</v>
+        <v>177.6282540957133</v>
       </c>
       <c r="F20" t="n">
         <v>1.122128649924875</v>
       </c>
       <c r="G20" t="n">
-        <v>0.482878913268512</v>
+        <v>0.4828789132685121</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5121951219512195</v>
+        <v>4.135044642857142</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5121951219512195</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5121951219512195</v>
+        <v>6.333240327380952</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5.719866071428571</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.478050595238095</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.135044642857142</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>0.824032738095238</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +1925,67 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.934860202260559</v>
+        <v>1499.886621315193</v>
       </c>
       <c r="D21" t="n">
-        <v>10.16038247434104</v>
+        <v>198.369372118087</v>
       </c>
       <c r="E21" t="n">
-        <v>9.049252021603468</v>
+        <v>176.6758728027344</v>
       </c>
       <c r="F21" t="n">
         <v>1.122786993895733</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4789818509984683</v>
+        <v>0.4789818509984682</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5121951219512195</v>
+        <v>4.611235119047619</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5121951219512195</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5121951219512195</v>
+        <v>6.36811755952381</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5.591517857142857</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.269717261904762</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4.611235119047619</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +1995,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1380,6 +2018,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/24/Filled_2D_sections/coronal/week24_coronal_Batch_Allmarks.xlsx
+++ b/measurements/24/Filled_2D_sections/coronal/week24_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2055,4 +2261,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week24_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1597.862811791383</v>
+      </c>
+      <c r="D10" t="n">
+        <v>36.15720694602083</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1499.886621315193</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1626.303854875283</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>211.2218989218984</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.955162045739264</v>
+      </c>
+      <c r="E11" t="n">
+        <v>198.369372118087</v>
+      </c>
+      <c r="F11" t="n">
+        <v>219.3894365287962</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.148838685444346</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01845798466230702</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.118375509112735</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.173701531027829</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4508924683129573</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.02133143268059214</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4226168541957873</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4874906462988245</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0089.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0091.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0092.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0093.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0095.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0096.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0097.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0099.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0100.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0101.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0103.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0104.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0105.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0107.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0108.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0109.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0111.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0112.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0113.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0114.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.4442616583193193</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3663475485325233</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.6386663736585051</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6708203932499369</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>23</v>
+      </c>
+      <c r="C48" t="n">
+        <v>10.52431094720497</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.6253671107732552</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.844866071428571</v>
+      </c>
+      <c r="F48" t="n">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>55</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.151041666666665</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.059151403376981</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.078497023809524</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7.756696428571428</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.193930697278911</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6536833703925623</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8147321428571428</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.514880952380952</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>